--- a/Packages/cn.etetet.gameplay/Assets/Editor/Luban/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.gameplay/Assets/Editor/Luban/Base/__tables__.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unityproject\Game\Develop\Packages\cn.etetet.gameplay\Assets\Editor\Luban\Base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B4C6EF2-F892-4231-9EF3-58778EBFD47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF5FF8E-4688-4B1C-A6AB-4D531D55F9C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -149,12 +149,14 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
